--- a/example/sample_input.xlsx
+++ b/example/sample_input.xlsx
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Budi Santoso</t>
+          <t>Example Target A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>081234567890</t>
+          <t>081200000001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>budi.santoso99@gmail.com</t>
+          <t>target_a@example.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -463,44 +463,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Siti Rahmawati</t>
+          <t>Example Target B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>085712345678</t>
+          <t>085700000002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>siti.rahma@yahoo.com</t>
+          <t>target_b@example.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Bandung</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi</t>
+          <t>Example Target C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>081987654321</t>
+          <t>081300000003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ahmad.fauzi@outlook.com</t>
+          <t>target_c@example.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bandung</t>
+          <t>Surabaya</t>
         </is>
       </c>
     </row>
